--- a/data/trans_orig/RUIDO_1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1_R-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27517</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39009</t>
+          <t>39070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>41884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56162</t>
+          <t>56379</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73032</t>
+          <t>73632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92013</t>
+          <t>91611</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>15018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26571</t>
+          <t>26223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30258</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34603</t>
+          <t>35005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53584</t>
+          <t>52984</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32358</t>
+          <t>32377</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41547</t>
+          <t>41490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32737</t>
+          <t>33078</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42856</t>
+          <t>42407</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67837</t>
+          <t>68752</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82288</t>
+          <t>82369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>28442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>20770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32970</t>
+          <t>32798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39988</t>
+          <t>39835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52015</t>
+          <t>51895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89944</t>
+          <t>90401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110341</t>
+          <t>110974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62852</t>
+          <t>63366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84824</t>
+          <t>85262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159680</t>
+          <t>160072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192207</t>
+          <t>193394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>29761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43042</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>32662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66376</t>
+          <t>65984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>35930</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52011</t>
+          <t>51631</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66040</t>
+          <t>65199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90899</t>
+          <t>91572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107305</t>
+          <t>107260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33782</t>
+          <t>33109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19476</t>
+          <t>20208</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27778</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26758</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36179</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50452</t>
+          <t>49629</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62458</t>
+          <t>61871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20670</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>239294</t>
+          <t>240636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>273873</t>
+          <t>273230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>266680</t>
+          <t>267597</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>300376</t>
+          <t>300609</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>516831</t>
+          <t>516359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>565561</t>
+          <t>563799</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54413</t>
+          <t>55056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88992</t>
+          <t>87650</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>79530</t>
+          <t>79297</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>113226</t>
+          <t>112309</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>142631</t>
+          <t>144393</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>191361</t>
+          <t>191833</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1_R-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46530</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39154</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52541</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33601</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27865</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39070</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>62,12%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41884</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56379</t>
+          <t>39560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>83399</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73632</t>
+          <t>71211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91611</t>
+          <t>88654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>16042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26223</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22731</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>15129</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>27620</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>43217</t>
+          <t>43256</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35005</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52984</t>
+          <t>52061</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>72528</t>
+          <t>54689</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72528</t>
+          <t>54689</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72528</t>
+          <t>54689</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36722</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30761</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41228</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>78,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>65,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>37418</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>32377</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>41490</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>77,25%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>66,84%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>37791</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>31787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42407</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>75790</t>
+          <t>74512</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68752</t>
+          <t>67003</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82369</t>
+          <t>80899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10342</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5836</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11020</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6948</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16061</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>33,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24157</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19408</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27822</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17879</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14079</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20770</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>73,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>13757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32798</t>
+          <t>20576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39835</t>
+          <t>35531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>46415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13333</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6585</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3694</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10385</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>26,92%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,45%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22689</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38059</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38059</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38059</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>70283</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58614</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>77958</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>60,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>79,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>100171</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>90401</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>110974</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>75,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>76464</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63366</t>
+          <t>63295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85262</t>
+          <t>76523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>176636</t>
+          <t>140939</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160072</t>
+          <t>127373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193394</t>
+          <t>150809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27370</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19695</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39039</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>39,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>19991</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9188</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29761</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>24,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29430</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20632</t>
+          <t>14268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42528</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>49420</t>
+          <t>47505</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32662</t>
+          <t>37635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65984</t>
+          <t>61071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>105894</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>105894</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>105894</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>56682</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>49653</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>61027</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>72,11%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>88,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>40933</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>35930</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44860</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>81,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>71,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>89,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59843</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65199</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>100776</t>
+          <t>94457</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91572</t>
+          <t>87054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107260</t>
+          <t>100756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12180</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7835</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>19209</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>9309</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5382</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14312</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>18,53%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28,49%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>21183</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17421</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33109</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>46778</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>46778</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74439</t>
+          <t>46778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>24050</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28021</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>25491</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36145</t>
+          <t>28937</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>54946</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49629</t>
+          <t>48579</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61871</t>
+          <t>60807</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7844</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3907</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13249</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>35,52%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>6222</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2871</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10684</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>20,14%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>34,58%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>12018</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14169</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21493</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>263828</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>247704</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>277589</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>74,91%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>70,33%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>78,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>254672</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>240636</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>273230</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>73,3%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>83,23%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>285302</t>
+          <t>222704</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>267597</t>
+          <t>208620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>300609</t>
+          <t>234148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>539974</t>
+          <t>486531</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>516359</t>
+          <t>467082</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>563799</t>
+          <t>504944</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>88374</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>74613</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>104498</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>25,09%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>21,18%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>29,67%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>73614</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>55056</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>87650</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>26,7%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>94604</t>
+          <t>74804</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>79297</t>
+          <t>63360</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112309</t>
+          <t>88888</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>168218</t>
+          <t>163178</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>144393</t>
+          <t>144765</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>191833</t>
+          <t>182627</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>463</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>379906</t>
+          <t>297508</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>379906</t>
+          <t>297508</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>379906</t>
+          <t>297508</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
